--- a/Result/profitability/3033.xlsx
+++ b/Result/profitability/3033.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.61625</v>
+        <v>0.7537499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>5.04125</v>
+        <v>5.15125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5325</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>5.17625</v>
+        <v>5.27625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>0.49625</v>
+        <v>0.6437499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5575</v>
+        <v>5.680000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0.44</v>
+        <v>0.7150000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>5.62125</v>
+        <v>6.2075</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,13 +1137,13 @@
         <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5449999999999999</v>
+        <v>0.69125</v>
       </c>
       <c r="N6" t="n">
-        <v>6.49</v>
+        <v>6.64</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5125000000000001</v>
+        <v>0.6475</v>
       </c>
       <c r="N7" t="n">
-        <v>6.6675</v>
+        <v>6.80125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.47</v>
       </c>
       <c r="M8" t="n">
-        <v>0.47375</v>
+        <v>0.51625</v>
       </c>
       <c r="N8" t="n">
-        <v>6.845</v>
+        <v>6.86125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>1.03</v>
       </c>
       <c r="M12" t="n">
-        <v>0.57875</v>
+        <v>0.5787500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>7.0975</v>
@@ -2026,10 +2026,10 @@
         <v>0.62</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6275000000000001</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>7.1</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3033</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>37629</v>
+      </c>
+      <c r="D75" t="n">
+        <v>35254</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2375</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1446</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-207</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1239</v>
+      </c>
+      <c r="K75" t="n">
+        <v>918</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.81875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.09125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2236842105263159</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.1299999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02103559870550153</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-6.470588235294118</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>2.895061728395061</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
